--- a/data/trans_dic/IP31KM16_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM16_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,99</t>
+          <t>3,96; 18,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 17,04</t>
+          <t>0,0; 11,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 10,96</t>
+          <t>2,88; 11,82</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,9; 21,63</t>
+          <t>9,42; 18,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,51; 18,06</t>
+          <t>10,54; 20,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,72; 18,27</t>
+          <t>11,33; 17,56</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 16,79</t>
+          <t>7,17; 15,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,6; 14,55</t>
+          <t>8,81; 17,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,53; 13,93</t>
+          <t>8,87; 14,66</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,83; 20,87</t>
+          <t>9,86; 23,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,94; 25,22</t>
+          <t>10,76; 18,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,91; 20,32</t>
+          <t>11,2; 19,2</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,63; 16,39</t>
+          <t>10,31; 16,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,22; 17,57</t>
+          <t>10,92; 15,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,07; 15,43</t>
+          <t>11,13; 15,0</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>4997</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4647</t>
+          <t>1483; 7071</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1589; 7716</t>
+          <t>0; 5062</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2404; 10059</t>
+          <t>2311; 9472</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>24506</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>24662</t>
+          <t>21374</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49169</t>
+          <t>42972</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17364; 34449</t>
+          <t>14789; 29363</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17309; 32870</t>
+          <t>15336; 29368</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39989; 62336</t>
+          <t>34281; 53124</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20746</t>
+          <t>21112</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21461</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42207</t>
+          <t>42795</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14666; 29052</t>
+          <t>14339; 30314</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14031; 30916</t>
+          <t>15382; 31397</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32886; 53723</t>
+          <t>33236; 54954</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>39670</t>
+          <t>41355</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>43725</t>
+          <t>36090</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83395</t>
+          <t>77445</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26951; 57235</t>
+          <t>28812; 68463</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30332; 76930</t>
+          <t>27481; 46870</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63183; 117682</t>
+          <t>61344; 105147</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>115</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>86218</t>
+          <t>87588</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>93761</t>
+          <t>80621</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179979</t>
+          <t>168208</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>69400; 107035</t>
+          <t>70780; 112471</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>76109; 130845</t>
+          <t>67528; 96009</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>154711; 215729</t>
+          <t>145236; 195757</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM16_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM16_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman golosinas o caramelos varias veces al día (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>3,96; 18,89</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,86</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2,88; 11,82</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>13,75%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>14,69%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>14,2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>9,42; 18,7</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10,54; 20,18</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11,33; 17,56</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>10,55%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>12,41%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>7,17; 15,15</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>8,81; 17,97</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>8,87; 14,66</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>14,15%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14,13%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14,14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>9,86; 23,43</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>10,76; 18,36</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11,2; 19,2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>12,75%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>10,31; 16,38</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10,92; 15,53</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11,13; 15,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.09411398107237989</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.03453558961684713</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.06237433053391326</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>3523</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1474</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4997</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.03960775315126187</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.02884680696962666</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1483; 7071</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5062</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2311; 9472</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1888794384540784</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1185979917922016</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1182316073412007</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1375297475603352</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1468806010135205</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1420270891637417</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>21598</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>21374</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>42972</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.09416941950328578</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1053891289549668</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.113303596983776</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>14789; 29363</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>15336; 29368</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>34281; 53124</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1869783081442401</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.2018168898789028</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1755801974974774</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1054917549503834</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1241365411781992</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1141810391895316</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>21112</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>21683</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>42795</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.07165062820980972</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.08806234940895778</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.08867597506934952</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>14339; 30314</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>15382; 31397</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>33236; 54954</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1514748661789581</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1797462048325066</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1466218425642624</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1415199836063416</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1413417408302885</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1414368654636564</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>41355</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>36090</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>77445</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.09859664768890761</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1076260332856875</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1120324602333807</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>28812; 68463</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>27481; 46870</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>61344; 105147</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.2342836788788164</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1835620116394705</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.192028603783233</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.1275259157882725</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1304104234553728</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1288923387306888</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>87588</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>80621</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>168208</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.1030546284068539</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.1092311941514348</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.111289398160339</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>70780; 112471</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>67528; 96009</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>145236; 195757</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.1637551334233364</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.1553020288256364</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.1500016334189465</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman golosinas o caramelos varias veces al día (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>3523</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1474</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>4997</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1483</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>7071</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>5062</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>9472</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>21598</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>21374</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>42972</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>14789</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>15336</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>34281</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>29363</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>29368</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>53124</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>21112</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>21683</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>42795</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>14339</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>15382</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>33236</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>30314</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>31397</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>54954</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>41355</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>36090</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>77445</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>28812</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>27481</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>61344</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>68463</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>46870</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>105147</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>87588</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>80621</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>168208</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>70780</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>67528</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>145236</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>112471</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>96009</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>195757</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>